--- a/02_DIA_inicio_2026_analisis_assets/rbd_9695_liceo-polivalente-eugenio-pereira-salas_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9695_liceo-polivalente-eugenio-pereira-salas_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35687D28-96F0-4F1B-B57D-D9E04FD1E080}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{519CB917-185D-4230-A273-73ACD9FE14FD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F707DF4-49A7-4CDB-9B55-FED89DD1764C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32A1745E-0D37-42C6-A52B-FBC95172B982}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DAA2FA8-825B-4D80-8F88-DA2EBABEB91C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28ADE556-3DCE-4DA3-8812-B307DB287938}"/>
 </file>